--- a/user_list.xlsx
+++ b/user_list.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/user_list.xlsx
+++ b/user_list.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -638,6 +638,33 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>U20260006</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Mayuri</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>mayuriashelke@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>0616</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>https://sgipl2026-lgtm.github.io/selection/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/user_list.xlsx
+++ b/user_list.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -638,33 +638,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>U20260006</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Mayuri</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>mayuriashelke@gmail.com</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>0616</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>https://sgipl2026-lgtm.github.io/selection/</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/user_list.xlsx
+++ b/user_list.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -638,6 +638,33 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>U20260006</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Mayuri</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>mayurirsurve@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>0616</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>https://sgipl2026-lgtm.github.io/selection/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/user_list.xlsx
+++ b/user_list.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -521,7 +521,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>0616</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -538,128 +538,20 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Rahul</t>
+          <t>Mayuri</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>rohit.surve@outlook.com</t>
+          <t>mayurirsurve@gmail.com</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>0616</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>https://sgipl2026-lgtm.github.io/selection/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>U20260003</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Priya</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>rohitmsurve2024@gmail.com</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>https://sgipl2026-lgtm.github.io/selection/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>U20260004</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Amit</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>ashokvshelke61@gmail.com</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>3456</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>https://sgipl2026-lgtm.github.io/selection/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>U20260005</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Rohit5</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>test@gmail.com</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>9999</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>https://sgipl2026-lgtm.github.io/selection/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>U20260006</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Mayuri</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>mayurirsurve@gmail.com</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>0616</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>https://sgipl2026-lgtm.github.io/selection/</t>
         </is>

--- a/user_list.xlsx
+++ b/user_list.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -557,6 +557,33 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>U20260003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Deepak</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>deepak_darole@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://sgipl2026-lgtm.github.io/selection/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
